--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_566_Nigeria.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_566_Nigeria.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rc0ce6442bfa64ae6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Ra8a49b7bfc724d1b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R55545201522c4168"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R983ff1b80d77462d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R0ae9a16804064258"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rfd2e0a07a84340f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rf32a14acbe314c99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rb7a49750b84b43b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R0b48b2fc23e54719"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R951499ac145a44ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R354bbdfc9ff8454c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R2c35c2ec19ed4a48"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ566CommercialTable" displayName="EEZ566CommercialTable" ref="A1:O11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O11"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ566CommercialTable" displayName="EEZ566CommercialTable" ref="A1:E11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E11"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ566FunctionalTable" displayName="EEZ566FunctionalTable" ref="A1:O19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O19"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ566FunctionalTable" displayName="EEZ566FunctionalTable" ref="A1:E19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E19"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ566ValidationTable" displayName="EEZ566ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ566ValidationTable" displayName="EEZ566ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -5853,7 +5807,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R395b2024374145da"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1650556e65f74c94"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5863,20 +5817,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -5884,606 +5828,212 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>4077.3190813456</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.5</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>3162.2776601683795</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>4077.3190813456</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>3162.2776601683795</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$78,A2,'Species'!$U$2:$U$78))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>12893615.04431745</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.5</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>3162.2776601683795</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>12893615.04431745</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>52232.5894789932</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.045261606098661</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>110.98431505044077</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>52232.5894789932</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>130.12343424209948</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$78,A3,'Species'!$U$2:$U$78))</x:f>
-        <x:v>6796683.922364349</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.045261606098661</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>110.98431505044077</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>5796998.166636919</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>999685.7557274299</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.1724488652559621</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.1724488652559622</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>9136.1704863628</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.360001668171918</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>229.0876452254261</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>9136.1704863628</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>229.08789684119205</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$78,A4,'Species'!$U$2:$U$78))</x:f>
-        <x:v>2092986.0819034246</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.360001668171918</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>229.0876452254261</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>2092983.7830988897</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>2.2988045348320156</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.000001098338436</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.0000010983384359664679</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>133286.4649288891</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>2.757954235593635</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>57.27356749594107</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>133286.4649288891</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>68.26270872272659</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$78,A5,'Species'!$U$2:$U$78))</x:f>
-        <x:v>9098495.13212267</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>2.757954235593635</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>57.27356749594107</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>7633791.345400112</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>1464703.7867225576</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.1918710795789753</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.19187107957897528</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>4906.8313372401</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.06</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>114.81536214968828</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>4906.8313372401</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>114.81536214968827</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$78,A6,'Species'!$U$2:$U$78))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>563379.6169926613</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.06</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>114.81536214968828</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>563379.6169926613</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>60330.864782906996</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.3259210686617577</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>211.79761663098319</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>60330.864782906996</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>260.2870645959943</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$78,A7,'Species'!$U$2:$U$78))</x:f>
-        <x:v>15703343.698880712</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.3259210686617577</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>211.79761663098319</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>12777933.370305821</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>2925410.3285748903</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.2289423683624103</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.2289423683624103</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>230569.7016186773</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.818580642748628</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>658.5377003432615</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>230569.7016186773</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>945.3832285004428</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$78,A8,'Species'!$U$2:$U$78))</x:f>
-        <x:v>217976728.9106489</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.818580642748628</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>658.5377003432615</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>151838841.07279572</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>66137887.83785319</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.4355795089752093</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.43557950897520925</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>8075.43</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.92</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>831.7637711026708</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>8075.43</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>831.7637711026708</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$78,A9,'Species'!$U$2:$U$78))</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>6716850.110075641</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.92</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>831.7637711026708</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
-        <x:v>6716850.110075641</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>26044.738834451204</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.8467887517227877</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>702.7304166215235</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>26044.738834451204</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>859.8360251228269</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$78,A10,'Species'!$U$2:$U$78))</x:f>
-        <x:v>22394204.71477665</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.8467887517227877</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>702.7304166215235</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>18302430.171932667</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>4091774.5428439826</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.223564548773356</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.22356454877335596</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>3609.778464294</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.45951076285012</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>2880.78444158008</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>3609.778464294</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>2892.0403264744045</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$78,A11,'Species'!$U$2:$U$78))</x:f>
-        <x:v>10439624.888377095</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.45951076285012</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>2880.78444158008</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>10398993.63748899</x:v>
       </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>40631.25088810548</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0039072291324063</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.003907229132406371</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G11">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O11">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R363f5f53700e47b8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8e43c56aa1f64481"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6493,20 +6043,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -6514,1038 +6054,364 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>601.1974384478</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.81</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>645.6542290346556</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>601.1974384478</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>645.6542290346556</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$78,A2,'Species'!$U$2:$U$78))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>388165.6686186241</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.81</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>645.6542290346556</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>388165.6686186241</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>6482.8184096889</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.398001423908314</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2500.3535595173394</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>6482.8184096889</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2531.0722810666025</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$78,A3,'Species'!$U$2:$U$78))</x:f>
-        <x:v>16408481.979951847</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.398001423908314</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2500.3535595173394</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>16209338.086370178</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>199143.89358166978</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0122857511220105</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.01228575112201049</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>106077.03747363441</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.86633176816418</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>735.0751956231487</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>106077.03747363441</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>757.7039869411275</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$78,A4,'Species'!$U$2:$U$78))</x:f>
-        <x:v>80374994.21667618</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.86633176816418</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>735.0751956231487</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>77974599.07205589</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>2400395.1446202844</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0307843217302355</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.030784321730235417</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>32510.701723353704</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.397514650517599</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2497.5526403322524</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>32510.701723353704</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2501.3275833702105</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$78,A5,'Species'!$U$2:$U$78))</x:f>
-        <x:v>81319914.97534606</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.397514650517599</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2497.5526403322524</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>81197188.92821635</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>122726.04712970555</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0015114568465935</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.0015114568465935862</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>9275.989348563799</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.4569144824070017</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>286.3614035750902</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>9275.989348563799</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>312.980455492702</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$78,A6,'Species'!$U$2:$U$78))</x:f>
-        <x:v>2903203.3714589495</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.4569144824070017</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>286.3614035750902</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>2656285.329402316</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>246918.04205663363</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0929561441775504</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.0929561441775504</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>8075.43</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.92</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>831.7637711026708</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>8075.43</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>831.7637711026708</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$78,A7,'Species'!$U$2:$U$78))</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>6716850.110075641</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.92</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>831.7637711026708</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
-        <x:v>6716850.110075641</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>16768.7494858874</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.062455970825557</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1154.664917762885</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>16768.7494858874</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1162.3407791810207</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$78,A8,'Species'!$U$2:$U$78))</x:f>
-        <x:v>19491001.343317702</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.062455970825557</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1154.664917762885</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>19362286.746108595</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>128714.59720910713</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0066476960545467</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.006647696054546657</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>4077.3190813456</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.5</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>3162.2776601683795</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>4077.3190813456</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>3162.2776601683795</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$78,A9,'Species'!$U$2:$U$78))</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>12893615.04431745</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.5</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>3162.2776601683795</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
-        <x:v>12893615.04431745</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>12471.348460144201</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.8917544638160537</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>779.3893441762328</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>12471.348460144201</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1022.9902660627678</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$78,A10,'Species'!$U$2:$U$78))</x:f>
-        <x:v>12758068.079404406</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.8917544638160537</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>779.3893441762328</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>9720036.09734506</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>3038031.9820593465</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.3125535699285271</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.31255356992852706</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>98984.415783107</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.4339789952823594</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>271.63078910242143</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>98984.415783107</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>306.0472939425765</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$78,A11,'Species'!$U$2:$U$78))</x:f>
-        <x:v>30293912.592906762</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.4339789952823594</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>271.63078910242143</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>26887214.968007535</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>3406697.624899227</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.1267032539053516</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.12670325390535153</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>75324.8417775965</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>2.8177462309370327</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>65.7273663782741</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>75324.8417775965</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>151.30877299611495</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$78,A12,'Species'!$U$2:$U$78))</x:f>
-        <x:v>11397309.385494625</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>2.8177462309370327</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>65.7273663782741</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>4950903.4729016125</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>6446405.912593013</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>2.3020665718644926</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>1.3020665718644924</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>27571.698264935098</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.2703081624451538</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>186.34088871844475</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>27571.698264935098</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>566.1102701083796</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$78,A13,'Species'!$U$2:$U$78))</x:f>
-        <x:v>15608621.55210915</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.2703081624451538</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>186.34088871844475</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>5137734.758164807</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>10470886.793944344</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>3.0380356882581716</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>2.0380356882581716</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>4906.8313372401</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.06</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>114.81536214968828</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>4906.8313372401</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>114.81536214968827</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$78,A14,'Species'!$U$2:$U$78))</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>563379.6169926613</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.06</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>114.81536214968828</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
-        <x:v>563379.6169926613</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>52232.5894789932</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.045261606098661</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>110.98431505044077</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>52232.5894789932</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>130.12343424209948</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$78,A15,'Species'!$U$2:$U$78))</x:f>
-        <x:v>6796683.922364349</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.045261606098661</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>110.98431505044077</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>5796998.166636919</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>999685.7557274299</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.1724488652559621</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.1724488652559622</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>24.4099057719</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.6199999999999997</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>416.8693834703351</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>24.4099057719</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>416.8693834703355</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$78,A16,'Species'!$U$2:$U$78))</x:f>
-        <x:v>10175.742369700936</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.6199999999999997</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>416.8693834703351</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>10175.742369700927</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>9.094947017729282e-12</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.0000000000000009</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>8.93787075900251e-16</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>4434.678777895399</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.1692654147328527</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>147.6608672215975</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>4434.678777895399</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>181.0594430696591</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$78,A17,'Species'!$U$2:$U$78))</x:f>
-        <x:v>802940.4697185775</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.1692654147328527</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>147.6608672215975</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>654828.5141932488</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>148111.95552532864</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.2261843403502413</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.22618434035024135</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>63313.6617801925</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>2.7782327507848015</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>60.01126075309922</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>63313.6617801925</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>60.89693533789104</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$78,A18,'Species'!$U$2:$U$78))</x:f>
-        <x:v>3855607.967433486</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>2.7782327507848015</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>60.01126075309922</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>3799532.6663246644</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>56075.30110882176</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.0147584732211459</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.014758473221145933</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>9136.1704863628</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.360001668171918</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>229.0876452254261</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>9136.1704863628</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>229.08789684119205</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$78,A19,'Species'!$U$2:$U$78))</x:f>
-        <x:v>2092986.0819034246</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.360001668171918</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>229.0876452254261</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>2092983.7830988897</x:v>
       </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>2.2988045348320156</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.000001098338436</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.0000010983384359664679</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G19">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O19">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc781110f54814c44"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd28c55034514ea6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7720,7 +6586,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -7819,7 +6685,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>304675912.12045956</x:v>
+        <x:v>229015816.3190449</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7833,7 +6699,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>304675912.12045956</x:v>
+        <x:v>277012116.7712002</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7847,7 +6713,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>-1.1920928955078125e-7</x:v>
+        <x:v>-75660095.80141479</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7861,7 +6727,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>-1.1920928955078125e-7</x:v>
+        <x:v>-27663795.349259496</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7872,9 +6738,9 @@
         <x:v>EEZ_566</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -7886,47 +6752,19 @@
         <x:v>EEZ_566</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_566</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_566</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R63c6940a575b4ac9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07c150e49f9a4a45"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7973,7 +6811,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
